--- a/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>01 SAN JUDAS TADEO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.06147</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.05125</v>
-      </c>
-      <c r="I2" t="n">
-        <v>290</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.06147</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.05125</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>02 MUNDO DE COLORES</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.05164</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.04826</v>
-      </c>
-      <c r="I3" t="n">
-        <v>234</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.05164</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.04826</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>0004 MARIANO MELGAR</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.06219</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.05445</v>
-      </c>
-      <c r="I4" t="n">
-        <v>542</v>
-      </c>
-      <c r="J4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.06219</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.05445</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>1003 REPUBLICA DE COLOMBIA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.05244</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.05322</v>
-      </c>
-      <c r="I5" t="n">
-        <v>285</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.05244</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.05322</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>1005 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.05624</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.04776</v>
-      </c>
-      <c r="I6" t="n">
-        <v>378</v>
-      </c>
-      <c r="J6" t="n">
-        <v>23</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.05624</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.04776</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>1006 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.05563</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.0446</v>
-      </c>
-      <c r="I7" t="n">
-        <v>467</v>
-      </c>
-      <c r="J7" t="n">
-        <v>23</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.05563</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.0446</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>1008 VIRGEN DE LOURDES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.05584</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.04707000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>377</v>
-      </c>
-      <c r="J8" t="n">
-        <v>22</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.05584</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.04707</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>0005 ROSA DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.053427</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.045407</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1476</v>
-      </c>
-      <c r="J9" t="n">
-        <v>96</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.053427</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.045407</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>1017 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.06122</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.05544999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>458</v>
-      </c>
-      <c r="J10" t="n">
-        <v>23</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.06122</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.05545</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>1019 CHAVIN</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.052576</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.04449</v>
-      </c>
-      <c r="I11" t="n">
-        <v>290</v>
-      </c>
-      <c r="J11" t="n">
-        <v>15</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.052576</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.04449</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>1014 REP. ORIENTAL DEL URUGUAY</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.05614</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.04789</v>
-      </c>
-      <c r="I12" t="n">
-        <v>366</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.05614</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.04789</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>MARIANO MELGAR</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.0599</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.05371</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1220</v>
-      </c>
-      <c r="J13" t="n">
-        <v>40</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.0599</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.05371</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>MIS AÑOS INOLVIDABLES</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.06502</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.05016999999999</v>
-      </c>
-      <c r="I14" t="n">
-        <v>226</v>
-      </c>
-      <c r="J14" t="n">
-        <v>20</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.06502</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.05017</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>LOS SANTOS APOSTOLES</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.05577</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.05253999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>321</v>
-      </c>
-      <c r="J15" t="n">
-        <v>24</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.05577</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.05254</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>PATROCINIO DE SAN JOSE</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.050105</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.050748</v>
-      </c>
-      <c r="I16" t="n">
-        <v>750</v>
-      </c>
-      <c r="J16" t="n">
-        <v>37</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.050105</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.050748</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>SANTISIMO SEÑOR DE LUREN</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.06608</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.05271</v>
-      </c>
-      <c r="I17" t="n">
-        <v>285</v>
-      </c>
-      <c r="J17" t="n">
-        <v>15</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.06608</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.05271</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SAN FRANCISCO JAVIER</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.05611</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.05155999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>365</v>
-      </c>
-      <c r="J18" t="n">
-        <v>22</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.05611</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.05156</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>ESPAÑA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.0583</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.04345000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>288</v>
-      </c>
-      <c r="J19" t="n">
-        <v>22</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.0583</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.04345</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>LUZ CASANOVA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.06027</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.05694</v>
-      </c>
-      <c r="I20" t="n">
-        <v>376</v>
-      </c>
-      <c r="J20" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.06027</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.05694</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>MARIA DE LA PROVIDENCIA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.06029</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.05591</v>
-      </c>
-      <c r="I21" t="n">
-        <v>302</v>
-      </c>
-      <c r="J21" t="n">
-        <v>28</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.06029</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.05591</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.06274</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.04491</v>
-      </c>
-      <c r="I22" t="n">
-        <v>699</v>
-      </c>
-      <c r="J22" t="n">
-        <v>40</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.06274</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.04491</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>LOS INGENIEROS DE LOS CEDROS</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.06454</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.04595999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.06454</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.04596</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.056921</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.055711</v>
-      </c>
-      <c r="I24" t="n">
-        <v>282</v>
-      </c>
-      <c r="J24" t="n">
-        <v>29</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.056921</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.055711</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>NUESTRA SEÑORA DEL BUEN CONSEJO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.05119</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.04844</v>
-      </c>
-      <c r="I25" t="n">
-        <v>692</v>
-      </c>
-      <c r="J25" t="n">
-        <v>75</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.05119</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.04844</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>295525</t>
+          <t>624357</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01 SAN JUDAS TADEO</t>
+          <t>LOS INGENIEROS DE LOS CEDROS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.06147</t>
+          <t>-12.06454</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.05125</t>
+          <t>-77.04596</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>295530</t>
+          <t>295525</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02 MUNDO DE COLORES</t>
+          <t>01 SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.05164</t>
+          <t>-12.06147</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.04826</t>
+          <t>-77.05125</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>295573</t>
+          <t>295530</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0004 MARIANO MELGAR</t>
+          <t>02 MUNDO DE COLORES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.06219</t>
+          <t>-12.05164</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.05445</t>
+          <t>-77.04826</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>295587</t>
+          <t>295672</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1003 REPUBLICA DE COLOMBIA</t>
+          <t>1019 CHAVIN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.05244</t>
+          <t>-12.052576</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.05322</t>
+          <t>-77.04449</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>295592</t>
+          <t>296068</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1005 JORGE CHAVEZ DARTNELL</t>
+          <t>SANTISIMO SEÑOR DE LUREN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.05624</t>
+          <t>-12.06608</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.04776</t>
+          <t>-77.05271</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>295605</t>
+          <t>295587</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1006 MARISCAL ANDRES AVELINO CACERES</t>
+          <t>1003 REPUBLICA DE COLOMBIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.05563</t>
+          <t>-12.05244</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.0446</t>
+          <t>-77.05322</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>295610</t>
+          <t>296134</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1008 VIRGEN DE LOURDES</t>
+          <t>LUZ CASANOVA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.05584</t>
+          <t>-12.06027</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.04707</t>
+          <t>-77.05694</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>376</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>295653</t>
+          <t>295733</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0005 ROSA DE SANTA MARIA</t>
+          <t>1014 REP. ORIENTAL DEL URUGUAY</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.053427</t>
+          <t>-12.05614</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.045407</t>
+          <t>-77.04789</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>295667</t>
+          <t>295931</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1017 SEÑOR DE LOS MILAGROS</t>
+          <t>MIS AÑOS INOLVIDABLES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.06122</t>
+          <t>-12.06502</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.05545</t>
+          <t>-77.05017</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>295672</t>
+          <t>295610</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1019 CHAVIN</t>
+          <t>1008 VIRGEN DE LOURDES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.052576</t>
+          <t>-12.05584</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.04449</t>
+          <t>-77.04707</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>377</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>295733</t>
+          <t>296073</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1014 REP. ORIENTAL DEL URUGUAY</t>
+          <t>SAN FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.05614</t>
+          <t>-12.05611</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.04789</t>
+          <t>-77.05156</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>365</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>295747</t>
+          <t>296105</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR</t>
+          <t>ESPAÑA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.0599</t>
+          <t>-12.0583</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.05371</t>
+          <t>-77.04345</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>295931</t>
+          <t>295592</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIS AÑOS INOLVIDABLES</t>
+          <t>1005 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.06502</t>
+          <t>-12.05624</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.05017</t>
+          <t>-77.04776</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>378</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>296011</t>
+          <t>295605</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LOS SANTOS APOSTOLES</t>
+          <t>1006 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.05577</t>
+          <t>-12.05563</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.05254</t>
+          <t>-77.0446</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>467</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>296030</t>
+          <t>295667</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PATROCINIO DE SAN JOSE</t>
+          <t>1017 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.050105</t>
+          <t>-12.06122</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.050748</t>
+          <t>-77.05545</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>458</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>296068</t>
+          <t>296011</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTISIMO SEÑOR DE LUREN</t>
+          <t>LOS SANTOS APOSTOLES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.06608</t>
+          <t>-12.05577</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.05271</t>
+          <t>-77.05254</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>321</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>296073</t>
+          <t>295573</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO JAVIER</t>
+          <t>0004 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.05611</t>
+          <t>-12.06219</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.05156</t>
+          <t>-77.05445</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>542</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>296105</t>
+          <t>296148</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
+          <t>MARIA DE LA PROVIDENCIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.0583</t>
+          <t>-12.06029</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.04345</t>
+          <t>-77.05591</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>302</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>296134</t>
+          <t>704170</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LUZ CASANOVA</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.06027</t>
+          <t>-12.056921</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.05694</t>
+          <t>-77.055711</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>296148</t>
+          <t>296030</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARIA DE LA PROVIDENCIA</t>
+          <t>PATROCINIO DE SAN JOSE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.06029</t>
+          <t>-12.050105</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.05591</t>
+          <t>-77.050748</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>750</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,27 +1741,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>296308</t>
+          <t>295747</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.06274</t>
+          <t>-12.0599</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.04491</t>
+          <t>-77.05371</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>624357</t>
+          <t>296308</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LOS INGENIEROS DE LOS CEDROS</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.06454</t>
+          <t>-12.06274</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.04596</t>
+          <t>-77.04491</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>699</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>704170</t>
+          <t>705301</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>NUESTRA SEÑORA DEL BUEN CONSEJO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.056921</t>
+          <t>-12.05119</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.055711</t>
+          <t>-77.04844</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>692</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>705301</t>
+          <t>295653</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL BUEN CONSEJO</t>
+          <t>0005 ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.05119</t>
+          <t>-12.053427</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.04844</t>
+          <t>-77.045407</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>624357</t>
+          <t>705301</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LOS INGENIEROS DE LOS CEDROS</t>
+          <t>NUESTRA SEÑORA DEL BUEN CONSEJO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.06454</t>
+          <t>692</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.04596</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.05119</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.04844</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>295525</t>
+          <t>704170</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01 SAN JUDAS TADEO</t>
+          <t>INTERNACIONAL ELIM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.06147</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.05125</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-12.056921</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.055711</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>295530</t>
+          <t>624357</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02 MUNDO DE COLORES</t>
+          <t>LOS INGENIEROS DE LOS CEDROS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.05164</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.04826</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-12.06454</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.04596</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>295672</t>
+          <t>296308</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1019 CHAVIN</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.052576</t>
+          <t>699</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.04449</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-12.06274</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.04491</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>296068</t>
+          <t>296148</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANTISIMO SEÑOR DE LUREN</t>
+          <t>MARIA DE LA PROVIDENCIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.06608</t>
+          <t>302</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.05271</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-12.06029</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.05591</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>295587</t>
+          <t>296134</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1003 REPUBLICA DE COLOMBIA</t>
+          <t>LUZ CASANOVA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.05244</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.05322</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-12.06027</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.05694</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>296134</t>
+          <t>296105</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LUZ CASANOVA</t>
+          <t>ESPAÑA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.06027</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.05694</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>-12.0583</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.04345</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>295733</t>
+          <t>296073</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1014 REP. ORIENTAL DEL URUGUAY</t>
+          <t>SAN FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.05614</t>
+          <t>365</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.04789</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>-12.05611</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.05156</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>295931</t>
+          <t>296068</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MIS AÑOS INOLVIDABLES</t>
+          <t>SANTISIMO SEÑOR DE LUREN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.06502</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.05017</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-12.06608</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.05271</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>295610</t>
+          <t>296030</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1008 VIRGEN DE LOURDES</t>
+          <t>PATROCINIO DE SAN JOSE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.05584</t>
+          <t>750</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.04707</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>-12.050105</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.050748</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>296073</t>
+          <t>296011</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO JAVIER</t>
+          <t>LOS SANTOS APOSTOLES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.05611</t>
+          <t>321</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.05156</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>-12.05577</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.05254</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>296105</t>
+          <t>295931</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ESPAÑA</t>
+          <t>MIS AÑOS INOLVIDABLES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.0583</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.04345</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-12.06502</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.05017</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>295592</t>
+          <t>295747</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1005 JORGE CHAVEZ DARTNELL</t>
+          <t>MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.05624</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.04776</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>-12.0599</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.05371</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>295605</t>
+          <t>295733</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1006 MARISCAL ANDRES AVELINO CACERES</t>
+          <t>1014 REP. ORIENTAL DEL URUGUAY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.05563</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.0446</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>-12.05614</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.04789</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>295667</t>
+          <t>295672</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1017 SEÑOR DE LOS MILAGROS</t>
+          <t>1019 CHAVIN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.06122</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.05545</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>-12.052576</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.04449</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>296011</t>
+          <t>295667</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LOS SANTOS APOSTOLES</t>
+          <t>1017 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.05577</t>
+          <t>458</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.05254</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>-12.06122</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.05545</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>295573</t>
+          <t>295653</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0004 MARIANO MELGAR</t>
+          <t>0005 ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.06219</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.05445</t>
+          <t>96</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>-12.053427</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.045407</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>296148</t>
+          <t>295610</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MARIA DE LA PROVIDENCIA</t>
+          <t>1008 VIRGEN DE LOURDES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.06029</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.05591</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>-12.05584</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.04707</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>704170</t>
+          <t>295605</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INTERNACIONAL ELIM</t>
+          <t>1006 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.056921</t>
+          <t>467</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.055711</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-12.05563</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.0446</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>296030</t>
+          <t>295592</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PATROCINIO DE SAN JOSE</t>
+          <t>1005 JORGE CHAVEZ DARTNELL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.050105</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.050748</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>-12.05624</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.04776</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>295747</t>
+          <t>295587</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR</t>
+          <t>1003 REPUBLICA DE COLOMBIA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.0599</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.05371</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>-12.05244</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-77.05322</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>296308</t>
+          <t>295573</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>0004 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.06274</t>
+          <t>542</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.04491</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>-12.06219</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-77.05445</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>705301</t>
+          <t>295530</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL BUEN CONSEJO</t>
+          <t>02 MUNDO DE COLORES</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.05119</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.04844</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>-12.05164</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-77.04826</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>295653</t>
+          <t>295525</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0005 ROSA DE SANTA MARIA</t>
+          <t>01 SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.053427</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.045407</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>-12.06147</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-77.05125</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-BREÑA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
